--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12225" windowHeight="4485"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FightScene" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -74,19 +74,25 @@
     <t>FightScene_Forest_1.prefab</t>
   </si>
   <si>
+    <t>#4C6820</t>
+  </si>
+  <si>
+    <t>#739025</t>
+  </si>
+  <si>
+    <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
+  </si>
+  <si>
+    <t>树林_1</t>
+  </si>
+  <si>
+    <t>FightScene_Test.prefab</t>
+  </si>
+  <si>
     <t>#111111</t>
   </si>
   <si>
     <t>#999999</t>
-  </si>
-  <si>
-    <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
-  </si>
-  <si>
-    <t>树林_1</t>
-  </si>
-  <si>
-    <t>FightScene_Test.prefab</t>
   </si>
   <si>
     <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
@@ -1157,16 +1163,16 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1,272 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FightScene" sheetId="1" r:id="rId1"/>
+    <sheet name="FightScene" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name_res</t>
-  </si>
-  <si>
-    <t>road_color_a</t>
-  </si>
-  <si>
-    <t>road_color_b</t>
-  </si>
-  <si>
-    <t>skybox_mat</t>
-  </si>
-  <si>
-    <t>remark</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>道路方格颜色1</t>
-  </si>
-  <si>
-    <t>道路方格颜色2</t>
-  </si>
-  <si>
-    <t>天空盒子</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>FightScene_Forest_1.prefab</t>
-  </si>
-  <si>
-    <t>#4C6820</t>
-  </si>
-  <si>
-    <t>#739025</t>
-  </si>
-  <si>
-    <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
-  </si>
-  <si>
-    <t>树林_1</t>
-  </si>
-  <si>
-    <t>FightScene_Test.prefab</t>
-  </si>
-  <si>
-    <t>#111111</t>
-  </si>
-  <si>
-    <t>#999999</t>
-  </si>
-  <si>
-    <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
-  </si>
-  <si>
-    <t>测试场景</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -566,158 +471,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -771,11 +677,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1064,143 +1033,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F82"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="4" width="47.5" customWidth="1"/>
-    <col min="5" max="5" width="74.375" customWidth="1"/>
-    <col min="6" max="6" width="42.875" customWidth="1"/>
-    <col min="7" max="7" width="25.125" customWidth="1"/>
+    <col width="47.5" customWidth="1" style="1" min="2" max="4"/>
+    <col width="74.375" customWidth="1" style="1" min="5" max="5"/>
+    <col width="42.875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="25.125" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_res</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>road_color_a</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>road_color_b</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>skybox_mat</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fog</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>道路方格颜色1</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>道路方格颜色2</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>天空盒子</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>雾配置</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Forest_1.prefab</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>#4C6820</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>#739025</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>树林_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Desert_1.prefab</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>#B8894C</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>#D9B36A</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/TFF_Skybox_Day_01A.mat</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>沙漠_1</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>10001</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Palace_1.prefab</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>#6B5B95</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>#B0A0D0</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/TFF_Skybox_Sunset_01A.mat</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>皇宫_BOSS_1</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>99999</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Test.prefab</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>#111111</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>#999999</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>测试场景</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>99999</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="12" customHeight="1"/>
-    <row r="82" ht="12" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1" s="1"/>
+    <row r="33" ht="15" customHeight="1" s="1"/>
+    <row r="34" ht="15" customHeight="1" s="1"/>
+    <row r="35" ht="15" customHeight="1" s="1"/>
+    <row r="36" ht="15" customHeight="1" s="1"/>
+    <row r="37" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1"/>
+    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="40" ht="15" customHeight="1" s="1"/>
+    <row r="41" ht="15" customHeight="1" s="1"/>
+    <row r="42" ht="15" customHeight="1" s="1"/>
+    <row r="74" ht="12" customHeight="1" s="1"/>
+    <row r="75" ht="12" customHeight="1" s="1"/>
+    <row r="76" ht="12" customHeight="1" s="1"/>
+    <row r="77" ht="12" customHeight="1" s="1"/>
+    <row r="78" ht="12" customHeight="1" s="1"/>
+    <row r="79" ht="12" customHeight="1" s="1"/>
+    <row r="80" ht="12" customHeight="1" s="1"/>
+    <row r="81" ht="12" customHeight="1" s="1"/>
+    <row r="82" ht="12" customHeight="1" s="1"/>
   </sheetData>
-  <sortState ref="A4:G88">
-    <sortCondition ref="A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1,177 +1,305 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="FightScene" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FightScene" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name_res</t>
+  </si>
+  <si>
+    <t>road_color_a</t>
+  </si>
+  <si>
+    <t>road_color_b</t>
+  </si>
+  <si>
+    <t>skybox_mat</t>
+  </si>
+  <si>
+    <t>fog</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>道路方格颜色1</t>
+  </si>
+  <si>
+    <t>道路方格颜色2</t>
+  </si>
+  <si>
+    <t>天空盒子</t>
+  </si>
+  <si>
+    <t>雾配置</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>FightScene_Forest_1.prefab</t>
+  </si>
+  <si>
+    <t>#4C6820</t>
+  </si>
+  <si>
+    <t>#739025</t>
+  </si>
+  <si>
+    <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
+  </si>
+  <si>
+    <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
+  </si>
+  <si>
+    <t>树林_1</t>
+  </si>
+  <si>
+    <t>FightScene_Desert_1.prefab</t>
+  </si>
+  <si>
+    <t>#B8894C</t>
+  </si>
+  <si>
+    <t>#D9B36A</t>
+  </si>
+  <si>
+    <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+  </si>
+  <si>
+    <t>沙漠_1</t>
+  </si>
+  <si>
+    <t>FightScene_Palace_1.prefab</t>
+  </si>
+  <si>
+    <t>#6B5B95</t>
+  </si>
+  <si>
+    <t>#B0A0D0</t>
+  </si>
+  <si>
+    <t>皇宫_BOSS_1</t>
+  </si>
+  <si>
+    <t>FightScene_Test.prefab</t>
+  </si>
+  <si>
+    <t>#111111</t>
+  </si>
+  <si>
+    <t>#999999</t>
+  </si>
+  <si>
+    <t>测试场景</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -471,159 +599,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -677,74 +805,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1033,278 +1098,192 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G82"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col width="47.5" customWidth="1" style="1" min="2" max="4"/>
-    <col width="74.375" customWidth="1" style="1" min="5" max="5"/>
-    <col width="42.875" customWidth="1" style="1" min="6" max="6"/>
-    <col width="25.125" customWidth="1" style="1" min="7" max="7"/>
+    <col min="2" max="4" width="47.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="74.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name_res</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>road_color_a</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>road_color_b</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>skybox_mat</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>fog</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>remark</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>道路方格颜色1</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>道路方格颜色2</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>天空盒子</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>雾配置</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:7">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Forest_1.prefab</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>#4C6820</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>#739025</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>树林_1</t>
-        </is>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:7">
+      <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Desert_1.prefab</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>#B8894C</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>#D9B36A</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/TFF_Skybox_Day_01A.mat</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>沙漠_1</t>
-        </is>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>10001</v>
       </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Palace_1.prefab</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>#6B5B95</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>#B0A0D0</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/TFF_Skybox_Sunset_01A.mat</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>皇宫_BOSS_1</t>
-        </is>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>99999</v>
       </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Test.prefab</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>#111111</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>#999999</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>测试场景</t>
-        </is>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="1"/>
-    <row r="33" ht="15" customHeight="1" s="1"/>
-    <row r="34" ht="15" customHeight="1" s="1"/>
-    <row r="35" ht="15" customHeight="1" s="1"/>
-    <row r="36" ht="15" customHeight="1" s="1"/>
-    <row r="37" ht="15" customHeight="1" s="1"/>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
-    <row r="40" ht="15" customHeight="1" s="1"/>
-    <row r="41" ht="15" customHeight="1" s="1"/>
-    <row r="42" ht="15" customHeight="1" s="1"/>
-    <row r="74" ht="12" customHeight="1" s="1"/>
-    <row r="75" ht="12" customHeight="1" s="1"/>
-    <row r="76" ht="12" customHeight="1" s="1"/>
-    <row r="77" ht="12" customHeight="1" s="1"/>
-    <row r="78" ht="12" customHeight="1" s="1"/>
-    <row r="79" ht="12" customHeight="1" s="1"/>
-    <row r="80" ht="12" customHeight="1" s="1"/>
-    <row r="81" ht="12" customHeight="1" s="1"/>
-    <row r="82" ht="12" customHeight="1" s="1"/>
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="74" ht="12" customHeight="1"/>
+    <row r="75" ht="12" customHeight="1"/>
+    <row r="76" ht="12" customHeight="1"/>
+    <row r="77" ht="12" customHeight="1"/>
+    <row r="78" ht="12" customHeight="1"/>
+    <row r="79" ht="12" customHeight="1"/>
+    <row r="80" ht="12" customHeight="1"/>
+    <row r="81" ht="12" customHeight="1"/>
+    <row r="82" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1,305 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FightScene" sheetId="1" r:id="rId1"/>
+    <sheet name="FightScene" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name_res</t>
-  </si>
-  <si>
-    <t>road_color_a</t>
-  </si>
-  <si>
-    <t>road_color_b</t>
-  </si>
-  <si>
-    <t>skybox_mat</t>
-  </si>
-  <si>
-    <t>fog</t>
-  </si>
-  <si>
-    <t>remark</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>道路方格颜色1</t>
-  </si>
-  <si>
-    <t>道路方格颜色2</t>
-  </si>
-  <si>
-    <t>天空盒子</t>
-  </si>
-  <si>
-    <t>雾配置</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>FightScene_Forest_1.prefab</t>
-  </si>
-  <si>
-    <t>#4C6820</t>
-  </si>
-  <si>
-    <t>#739025</t>
-  </si>
-  <si>
-    <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
-  </si>
-  <si>
-    <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
-  </si>
-  <si>
-    <t>树林_1</t>
-  </si>
-  <si>
-    <t>FightScene_Desert_1.prefab</t>
-  </si>
-  <si>
-    <t>#B8894C</t>
-  </si>
-  <si>
-    <t>#D9B36A</t>
-  </si>
-  <si>
-    <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
-  </si>
-  <si>
-    <t>沙漠_1</t>
-  </si>
-  <si>
-    <t>FightScene_Palace_1.prefab</t>
-  </si>
-  <si>
-    <t>#6B5B95</t>
-  </si>
-  <si>
-    <t>#B0A0D0</t>
-  </si>
-  <si>
-    <t>皇宫_BOSS_1</t>
-  </si>
-  <si>
-    <t>FightScene_Test.prefab</t>
-  </si>
-  <si>
-    <t>#111111</t>
-  </si>
-  <si>
-    <t>#999999</t>
-  </si>
-  <si>
-    <t>测试场景</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -599,159 +471,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -805,11 +677,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1098,192 +1033,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="4" width="47.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="74.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="1" customWidth="1"/>
+    <col width="47.5" customWidth="1" style="1" min="2" max="4"/>
+    <col width="74.375" customWidth="1" style="1" min="5" max="5"/>
+    <col width="42.875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="25.125" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name_res</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>road_color_a</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>road_color_b</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>skybox_mat</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>skybox_rotate</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>fog</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>道路方格颜色1</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>道路方格颜色2</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>天空盒子</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>天空盒旋转</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>雾配置</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Forest_1.prefab</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>#4C6820</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>#739025</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>树林_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Desert_1.prefab</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>#B8894C</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>#D9B36A</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>沙漠_1</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>10001</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Palace_1.prefab</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>#6B5B95</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>#B0A0D0</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>皇宫_BOSS_1</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>99999</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>FightScene_Test.prefab</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>#111111</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>#999999</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>测试场景</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>10001</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>99999</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="12" customHeight="1"/>
-    <row r="82" ht="12" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1" s="1"/>
+    <row r="33" ht="15" customHeight="1" s="1"/>
+    <row r="34" ht="15" customHeight="1" s="1"/>
+    <row r="35" ht="15" customHeight="1" s="1"/>
+    <row r="36" ht="15" customHeight="1" s="1"/>
+    <row r="37" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1"/>
+    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="40" ht="15" customHeight="1" s="1"/>
+    <row r="41" ht="15" customHeight="1" s="1"/>
+    <row r="42" ht="15" customHeight="1" s="1"/>
+    <row r="74" ht="12" customHeight="1" s="1"/>
+    <row r="75" ht="12" customHeight="1" s="1"/>
+    <row r="76" ht="12" customHeight="1" s="1"/>
+    <row r="77" ht="12" customHeight="1" s="1"/>
+    <row r="78" ht="12" customHeight="1" s="1"/>
+    <row r="79" ht="12" customHeight="1" s="1"/>
+    <row r="80" ht="12" customHeight="1" s="1"/>
+    <row r="81" ht="12" customHeight="1" s="1"/>
+    <row r="82" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1073,7 +1073,7 @@
           <t>skybox_mat</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>skybox_rotate</t>
         </is>
@@ -1115,7 +1115,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1157,7 +1157,7 @@
           <t>天空盒子</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>天空盒旋转</t>
         </is>
@@ -1197,7 +1197,7 @@
           <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
@@ -1237,9 +1237,14 @@
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Color:#F1D890&amp;Start:0&amp;End:100&amp;Mode:Linear</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -1272,7 +1277,7 @@
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
@@ -1307,7 +1312,7 @@
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1175,7 +1175,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>1</v>
+        <v>10001</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>2</v>
+        <v>20001</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Color:#F1D890&amp;Start:0&amp;End:100&amp;Mode:Linear</t>
         </is>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>10001</v>
+        <v>30001</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -19,14 +19,12 @@
   <fonts count="20">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
       <u val="single"/>
@@ -34,7 +32,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
       <u val="single"/>
@@ -42,14 +39,12 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
@@ -57,7 +52,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
@@ -65,7 +59,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
@@ -73,7 +66,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
@@ -81,7 +73,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
@@ -89,14 +80,12 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
@@ -104,7 +93,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
@@ -112,7 +100,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -120,14 +107,12 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -135,35 +120,30 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -471,22 +451,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -495,7 +475,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -619,11 +599,161 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1038,311 +1168,437 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="47.5" customWidth="1" style="1" min="2" max="4"/>
-    <col width="74.375" customWidth="1" style="1" min="5" max="5"/>
-    <col width="42.875" customWidth="1" style="1" min="6" max="6"/>
-    <col width="25.125" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.375" customWidth="1" style="50" min="2" max="2"/>
+    <col width="14" customWidth="1" style="50" min="3" max="4"/>
+    <col width="51.5" customWidth="1" style="50" min="5" max="5"/>
+    <col width="14.875" customWidth="1" style="50" min="6" max="6"/>
+    <col width="46" customWidth="1" style="50" min="7" max="7"/>
+    <col width="23.625" customWidth="1" style="50" min="8" max="8"/>
+    <col width="12.375" customWidth="1" style="50" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>name_res</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>road_color_a</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>road_color_b</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>skybox_mat</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="F1" s="49" t="inlineStr">
         <is>
           <t>skybox_rotate</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="G1" s="49" t="inlineStr">
         <is>
           <t>fog</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>volumetric_fog</t>
+        </is>
+      </c>
+      <c r="I1" s="49" t="inlineStr">
+        <is>
+          <t>ambient_light</t>
+        </is>
+      </c>
+      <c r="J1" s="49" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="K1" s="49" t="inlineStr">
+        <is>
+          <t>environment_sound</t>
+        </is>
+      </c>
+      <c r="L1" s="49" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="G2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" s="49" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" s="49" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" s="49" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="L2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>道路方格颜色1</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>道路方格颜色2</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>天空盒子</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" s="49" t="inlineStr">
         <is>
           <t>天空盒旋转</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="G3" s="49" t="inlineStr">
         <is>
           <t>雾配置</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>体积雾配置(形如Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1,空=不开启)</t>
+        </is>
+      </c>
+      <c r="I3" s="49" t="inlineStr">
+        <is>
+          <t>环境光颜色(如#364863,空=不修改)</t>
+        </is>
+      </c>
+      <c r="J3" s="49" t="inlineStr">
+        <is>
+          <t>场景细节预制(Details下同名子预制)</t>
+        </is>
+      </c>
+      <c r="K3" s="49" t="inlineStr">
+        <is>
+          <t>环境音(AudioInfo表id, 空或0=不播放)</t>
+        </is>
+      </c>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="49" t="n">
         <v>10001</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>FightScene_Forest_1.prefab</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>#4C6820</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>#739025</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>树林_1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>20001</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Desert_1.prefab</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>#B8894C</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>#D9B36A</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="A5" s="49" t="n">
+        <v>10002</v>
+      </c>
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>FightScene_Forest_1.prefab</t>
+        </is>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>#4C6820</t>
+        </is>
+      </c>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>#739025</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
+        </is>
+      </c>
+      <c r="F5" s="49" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>Color:#F1D890&amp;Start:0&amp;End:100&amp;Mode:Linear</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>沙漠_1</t>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>Color:#101A30&amp;Start:6&amp;End:16&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="inlineStr">
+        <is>
+          <t>#AABFE0</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="K5" s="49" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="L5" s="49" t="inlineStr">
+        <is>
+          <t>树林_1_夜晚</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n">
-        <v>30001</v>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>FightScene_Palace_1.prefab</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>#6B5B95</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>#B0A0D0</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="A6" s="49" t="n">
+        <v>20001</v>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>FightScene_Desert_1.prefab</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>#B8894C</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>#D9B36A</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>皇宫_BOSS_1</t>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>Color:#F1D890&amp;Start:0&amp;End:100&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="L6" s="49" t="inlineStr">
+        <is>
+          <t>沙漠_1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="49" t="n">
+        <v>30001</v>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>FightScene_Palace_1.prefab</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>#6B5B95</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>#B0A0D0</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="L7" s="49" t="inlineStr">
+        <is>
+          <t>皇宫_BOSS_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="n">
         <v>99999</v>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>FightScene_Test.prefab</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>#111111</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>#999999</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="L8" s="49" t="inlineStr">
         <is>
           <t>测试场景</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="1"/>
-    <row r="33" ht="15" customHeight="1" s="1"/>
-    <row r="34" ht="15" customHeight="1" s="1"/>
-    <row r="35" ht="15" customHeight="1" s="1"/>
-    <row r="36" ht="15" customHeight="1" s="1"/>
-    <row r="37" ht="15" customHeight="1" s="1"/>
-    <row r="38" ht="15" customHeight="1" s="1"/>
-    <row r="39" ht="15" customHeight="1" s="1"/>
-    <row r="40" ht="15" customHeight="1" s="1"/>
-    <row r="41" ht="15" customHeight="1" s="1"/>
-    <row r="42" ht="15" customHeight="1" s="1"/>
-    <row r="74" ht="12" customHeight="1" s="1"/>
-    <row r="75" ht="12" customHeight="1" s="1"/>
-    <row r="76" ht="12" customHeight="1" s="1"/>
-    <row r="77" ht="12" customHeight="1" s="1"/>
-    <row r="78" ht="12" customHeight="1" s="1"/>
-    <row r="79" ht="12" customHeight="1" s="1"/>
-    <row r="80" ht="12" customHeight="1" s="1"/>
-    <row r="81" ht="12" customHeight="1" s="1"/>
-    <row r="82" ht="12" customHeight="1" s="1"/>
+    <row r="33" ht="15" customHeight="1" s="50"/>
+    <row r="34" ht="15" customHeight="1" s="50"/>
+    <row r="35" ht="15" customHeight="1" s="50"/>
+    <row r="36" ht="15" customHeight="1" s="50"/>
+    <row r="37" ht="15" customHeight="1" s="50"/>
+    <row r="38" ht="15" customHeight="1" s="50"/>
+    <row r="39" ht="15" customHeight="1" s="50"/>
+    <row r="40" ht="15" customHeight="1" s="50"/>
+    <row r="41" ht="15" customHeight="1" s="50"/>
+    <row r="42" ht="15" customHeight="1" s="50"/>
+    <row r="43" ht="15" customHeight="1" s="50"/>
+    <row r="75" ht="12" customHeight="1" s="50"/>
+    <row r="76" ht="12" customHeight="1" s="50"/>
+    <row r="77" ht="12" customHeight="1" s="50"/>
+    <row r="78" ht="12" customHeight="1" s="50"/>
+    <row r="79" ht="12" customHeight="1" s="50"/>
+    <row r="80" ht="12" customHeight="1" s="50"/>
+    <row r="81" ht="12" customHeight="1" s="50"/>
+    <row r="82" ht="12" customHeight="1" s="50"/>
+    <row r="83" ht="12" customHeight="1" s="50"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -1655,42 +1655,42 @@
       <c r="A9" s="51" t="n">
         <v>20002</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>FightScene_Desert_1.prefab</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>#B8894C</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>#D9B36A</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="50" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="50" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:26&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="50" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="50" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="C10" s="51" t="inlineStr">
         <is>
-          <t>#6B5B95</t>
+          <t>#FFFFFF1A</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>#B0A0D0</t>
+          <t>#3F3F3F1A</t>
         </is>
       </c>
       <c r="E10" s="51" t="inlineStr">
@@ -1741,6 +1741,21 @@
       <c r="F10" s="51" t="inlineStr">
         <is>
           <t>-15,0,0</t>
+        </is>
+      </c>
+      <c r="G10" s="50" t="inlineStr">
+        <is>
+          <t>Color:#E3D3B3&amp;Start:18&amp;End:55&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="I10" s="50" t="inlineStr">
+        <is>
+          <t>#C4AF8E</t>
+        </is>
+      </c>
+      <c r="L10" s="50" t="inlineStr">
+        <is>
+          <t>mode:Bokeh&amp;length:220&amp;aperture:12</t>
         </is>
       </c>
       <c r="M10" s="51" t="inlineStr">
@@ -1788,37 +1803,37 @@
       <c r="A12" s="50" t="n">
         <v>40001</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="50" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="50" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="50" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_3.mat</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="50" t="inlineStr">
         <is>
           <t>Color:#D4F0FF&amp;Start:10&amp;End:150&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" s="50" t="inlineStr"/>
       <c r="J12" s="50" t="inlineStr">
         <is>
           <t>Day</t>
@@ -1839,42 +1854,42 @@
       <c r="A13" s="50" t="n">
         <v>40002</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="50" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:16&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="50" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="50" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
@@ -1902,32 +1917,32 @@
       <c r="A14" s="50" t="n">
         <v>40003</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="50" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="50" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="50" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_3.mat</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="50" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="50" t="inlineStr">
         <is>
           <t>Color:#F2E8FB&amp;Start:10&amp;End:28&amp;Mode:Linear</t>
         </is>
@@ -1952,42 +1967,42 @@
       <c r="A15" s="50" t="n">
         <v>40004</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="50" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:20&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="50" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="50" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_scene[战斗场景].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FightScene" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,15 +16,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
       <u val="single"/>
@@ -32,6 +34,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
       <u val="single"/>
@@ -39,12 +42,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
@@ -52,6 +57,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
@@ -59,6 +65,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
@@ -66,6 +73,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
@@ -73,6 +81,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
@@ -80,12 +89,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
@@ -93,6 +104,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
@@ -100,6 +112,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -107,12 +120,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -120,31 +135,29 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -451,22 +464,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -475,7 +488,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -529,10 +542,10 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
@@ -541,10 +554,10 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
@@ -553,10 +566,10 @@
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
@@ -565,10 +578,10 @@
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
@@ -577,10 +590,10 @@
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
@@ -589,170 +602,17 @@
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="37">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="41">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="43">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="44">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="45">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="46">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="47">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="48">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1174,878 +1034,935 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="29.375" customWidth="1" style="52" min="2" max="2"/>
-    <col width="14" customWidth="1" style="52" min="3" max="4"/>
-    <col width="51.5" customWidth="1" style="52" min="5" max="5"/>
-    <col width="14.875" customWidth="1" style="52" min="6" max="6"/>
-    <col width="46" customWidth="1" style="52" min="7" max="7"/>
-    <col width="23.625" customWidth="1" style="52" min="8" max="8"/>
-    <col width="12.375" customWidth="1" style="52" min="9" max="9"/>
+    <col width="29.375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14" customWidth="1" style="1" min="3" max="4"/>
+    <col width="51.5" customWidth="1" style="1" min="5" max="5"/>
+    <col width="14.875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="46" customWidth="1" style="1" min="7" max="7"/>
+    <col width="23.625" customWidth="1" style="1" min="8" max="8"/>
+    <col width="12.375" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>name_res</t>
         </is>
       </c>
-      <c r="C1" s="51" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>road_color_a</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>road_color_b</t>
         </is>
       </c>
-      <c r="E1" s="51" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>road_alpha</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>skybox_mat</t>
         </is>
       </c>
-      <c r="F1" s="51" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>skybox_rotate</t>
         </is>
       </c>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>fog</t>
         </is>
       </c>
-      <c r="H1" s="51" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>volumetric_fog</t>
         </is>
       </c>
-      <c r="I1" s="51" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>ambient_light</t>
         </is>
       </c>
-      <c r="J1" s="51" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>details</t>
         </is>
       </c>
-      <c r="K1" s="51" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>environment_sound</t>
         </is>
       </c>
-      <c r="L1" s="51" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>depth_of_field</t>
         </is>
       </c>
-      <c r="M1" s="51" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="B2" s="51" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="51" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="51" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="51" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="51" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="51" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="51" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="51" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="L2" s="51" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="51" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" s="51" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C3" s="51" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>道路方格颜色1</t>
         </is>
       </c>
-      <c r="D3" s="51" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>道路方格颜色2</t>
         </is>
       </c>
-      <c r="E3" s="51" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>道路透明度(0~1, 空默认0.5)</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>天空盒子</t>
         </is>
       </c>
-      <c r="F3" s="51" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>天空盒旋转</t>
         </is>
       </c>
-      <c r="G3" s="51" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>雾配置</t>
         </is>
       </c>
-      <c r="H3" s="51" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>体积雾配置(形如Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1,空=不开启)</t>
         </is>
       </c>
-      <c r="I3" s="51" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>环境光颜色(如#364863,空=不修改)</t>
         </is>
       </c>
-      <c r="J3" s="51" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>场景细节预制(Details下同名子预制)</t>
         </is>
       </c>
-      <c r="K3" s="51" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>环境音(AudioInfo表id, 空或0=不播放)</t>
         </is>
       </c>
-      <c r="L3" s="51" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>景深配置(形如mode:Bokeh&amp;length:130&amp;aperture:12,空=默认Bokeh/180/12)</t>
         </is>
       </c>
-      <c r="M3" s="51" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="n">
+      <c r="A4" s="0" t="n">
         <v>10001</v>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>FightScene_Forest_1.prefab</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>#4C6820</t>
         </is>
       </c>
-      <c r="D4" s="51" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>#739025</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_1.mat</t>
         </is>
       </c>
-      <c r="F4" s="53" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>Color:#CEF9FF&amp;Start:8&amp;End:20&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="M4" s="51" t="inlineStr">
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t>树林_1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="n">
+      <c r="A5" s="0" t="n">
         <v>10002</v>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>FightScene_Forest_1.prefab</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>#4C6820</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>#739025</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G5" s="51" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:16&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I5" s="51" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
       </c>
-      <c r="J5" s="51" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="K5" s="51" t="n">
+      <c r="L5" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="M5" s="51" t="inlineStr">
+      <c r="N5" s="0" t="inlineStr">
         <is>
           <t>树林_1_夜晚</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="n">
+      <c r="A6" s="0" t="n">
         <v>10003</v>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>FightScene_Forest_1.prefab</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>#4C6820</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>#739025</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_4.mat</t>
         </is>
       </c>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G6" s="51" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>Color:#9FB6C2&amp;Start:5&amp;End:15&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="I6" s="51" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>#93A5B1</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>DayRain</t>
         </is>
       </c>
-      <c r="K6" s="51" t="n">
+      <c r="L6" s="0" t="n">
         <v>2000002</v>
       </c>
-      <c r="M6" s="51" t="inlineStr">
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>树林_1_白天_下雨</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="0" t="n">
         <v>10004</v>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>FightScene_Forest_1.prefab</t>
         </is>
       </c>
-      <c r="C7" s="51" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>#4C6820</t>
         </is>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>#739025</t>
         </is>
       </c>
-      <c r="E7" s="51" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G7" s="51" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:16&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H7" s="51" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I7" s="51" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>#8A9CBD</t>
         </is>
       </c>
-      <c r="J7" s="51" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>NightLight</t>
         </is>
       </c>
-      <c r="K7" s="51" t="n">
+      <c r="L7" s="0" t="n">
         <v>2000002</v>
       </c>
-      <c r="M7" s="51" t="inlineStr">
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t>树林_1_夜晚_下雨</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="0" t="n">
         <v>20001</v>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>FightScene_Desert_1.prefab</t>
         </is>
       </c>
-      <c r="C8" s="51" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>#B8894C</t>
         </is>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>#D9B36A</t>
         </is>
       </c>
-      <c r="E8" s="51" t="inlineStr">
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F8" s="51" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G8" s="51" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Color:#F1D890&amp;Start:0&amp;End:100&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="J8" s="51" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="L8" s="51" t="inlineStr">
+      <c r="M8" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M8" s="51" t="inlineStr">
+      <c r="N8" s="0" t="inlineStr">
         <is>
           <t>沙漠_1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="0" t="n">
         <v>20002</v>
       </c>
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>FightScene_Desert_1.prefab</t>
         </is>
       </c>
-      <c r="C9" s="50" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>#B8894C</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>#D9B36A</t>
         </is>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:26&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H9" s="50" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I9" s="50" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
       </c>
-      <c r="J9" s="51" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="K9" s="51" t="n">
+      <c r="L9" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="L9" s="51" t="inlineStr">
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M9" s="51" t="inlineStr">
+      <c r="N9" s="0" t="inlineStr">
         <is>
           <t>沙漠_1_夜晚</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="0" t="n">
         <v>30001</v>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>FightScene_Palace_1.prefab</t>
         </is>
       </c>
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>#FFFFFF1A</t>
         </is>
       </c>
-      <c r="D10" s="51" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>#3F3F3F1A</t>
         </is>
       </c>
-      <c r="E10" s="51" t="inlineStr">
-        <is>
-          <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
-        </is>
-      </c>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G10" s="50" t="inlineStr">
-        <is>
-          <t>Color:#E3D3B3&amp;Start:18&amp;End:55&amp;Mode:Linear</t>
-        </is>
-      </c>
-      <c r="I10" s="50" t="inlineStr">
-        <is>
-          <t>#C4AF8E</t>
-        </is>
-      </c>
-      <c r="L10" s="50" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>Color:#241F22&amp;Start:10&amp;End:30&amp;Mode:Linear</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Distance:48&amp;Density:0.04&amp;Tint:#9A8570&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>#3F3630</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="n"/>
+      <c r="M10" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:220&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M10" s="51" t="inlineStr">
+      <c r="N10" s="0" t="inlineStr">
         <is>
           <t>皇宫_BOSS_1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="0" t="n">
         <v>99999</v>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>FightScene_Test.prefab</t>
         </is>
       </c>
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>#111111</t>
         </is>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>#999999</t>
         </is>
       </c>
-      <c r="E11" s="51" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_2.mat</t>
         </is>
       </c>
-      <c r="F11" s="51" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="M11" s="51" t="inlineStr">
+      <c r="N11" s="0" t="inlineStr">
         <is>
           <t>测试场景</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="0" t="n">
         <v>40001</v>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E12" s="50" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_3.mat</t>
         </is>
       </c>
-      <c r="F12" s="50" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G12" s="50" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Color:#D4F0FF&amp;Start:10&amp;End:150&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="I12" s="50" t="inlineStr"/>
-      <c r="J12" s="50" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr"/>
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="L12" s="50" t="inlineStr">
+      <c r="M12" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M12" s="50" t="inlineStr">
+      <c r="N12" s="0" t="inlineStr">
         <is>
           <t>平原_1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="0" t="n">
         <v>40002</v>
       </c>
-      <c r="B13" s="50" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E13" s="50" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G13" s="50" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:16&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H13" s="50" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I13" s="50" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
       </c>
-      <c r="J13" s="50" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="L13" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="L13" s="50" t="inlineStr">
+      <c r="M13" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M13" s="50" t="inlineStr">
+      <c r="N13" s="0" t="inlineStr">
         <is>
           <t>平原_1_夜晚</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="0" t="n">
         <v>40003</v>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C14" s="50" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D14" s="50" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E14" s="50" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_3.mat</t>
         </is>
       </c>
-      <c r="F14" s="50" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G14" s="50" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Color:#F2E8FB&amp;Start:10&amp;End:28&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="J14" s="50" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>DayFlowerSea</t>
         </is>
       </c>
-      <c r="L14" s="50" t="inlineStr">
+      <c r="M14" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M14" s="50" t="inlineStr">
+      <c r="N14" s="0" t="inlineStr">
         <is>
           <t>平原_1_白天花海</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="0" t="n">
         <v>40004</v>
       </c>
-      <c r="B15" s="50" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>FightScene_Plain_1.prefab</t>
         </is>
       </c>
-      <c r="C15" s="50" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>#337A0E</t>
         </is>
       </c>
-      <c r="D15" s="50" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>#4FA316</t>
         </is>
       </c>
-      <c r="E15" s="50" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>Assets/FrameWork/Materials/Skybox/Skybox_6.mat</t>
         </is>
       </c>
-      <c r="F15" s="50" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>-15,0,0</t>
         </is>
       </c>
-      <c r="G15" s="50" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>Color:#101A30&amp;Start:6&amp;End:20&amp;Mode:Linear</t>
         </is>
       </c>
-      <c r="H15" s="50" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>Distance:48&amp;Density:0.06&amp;Tint:#B8CCFF&amp;Scattering:0.05&amp;Anisotropy:0.5&amp;Attenuation:96&amp;BaseHeight:0&amp;MaxHeight:12&amp;MainLight:1&amp;AdditionalLight:1</t>
         </is>
       </c>
-      <c r="I15" s="50" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>#AABFE0</t>
         </is>
       </c>
-      <c r="J15" s="50" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>NightFlowerSea</t>
         </is>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="L15" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="L15" s="50" t="inlineStr">
+      <c r="M15" s="0" t="inlineStr">
         <is>
           <t>mode:Bokeh&amp;length:180&amp;aperture:12</t>
         </is>
       </c>
-      <c r="M15" s="50" t="inlineStr">
+      <c r="N15" s="0" t="inlineStr">
         <is>
           <t>平原_1_夜晚花海</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="52"/>
-    <row r="34" ht="15" customHeight="1" s="52"/>
-    <row r="35" ht="15" customHeight="1" s="52"/>
-    <row r="36" ht="15" customHeight="1" s="52"/>
-    <row r="37" ht="15" customHeight="1" s="52"/>
-    <row r="38" ht="15" customHeight="1" s="52"/>
-    <row r="39" ht="15" customHeight="1" s="52"/>
-    <row r="40" ht="15" customHeight="1" s="52"/>
-    <row r="41" ht="15" customHeight="1" s="52"/>
-    <row r="42" ht="15" customHeight="1" s="52"/>
-    <row r="43" ht="15" customHeight="1" s="52"/>
-    <row r="75" ht="12" customHeight="1" s="52"/>
-    <row r="76" ht="12" customHeight="1" s="52"/>
-    <row r="77" ht="12" customHeight="1" s="52"/>
-    <row r="78" ht="12" customHeight="1" s="52"/>
-    <row r="79" ht="12" customHeight="1" s="52"/>
-    <row r="80" ht="12" customHeight="1" s="52"/>
-    <row r="81" ht="12" customHeight="1" s="52"/>
-    <row r="82" ht="12" customHeight="1" s="52"/>
-    <row r="83" ht="12" customHeight="1" s="52"/>
+    <row r="33" ht="15" customHeight="1" s="1"/>
+    <row r="34" ht="15" customHeight="1" s="1"/>
+    <row r="35" ht="15" customHeight="1" s="1"/>
+    <row r="36" ht="15" customHeight="1" s="1"/>
+    <row r="37" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1"/>
+    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="40" ht="15" customHeight="1" s="1"/>
+    <row r="41" ht="15" customHeight="1" s="1"/>
+    <row r="42" ht="15" customHeight="1" s="1"/>
+    <row r="43" ht="15" customHeight="1" s="1"/>
+    <row r="75" ht="12" customHeight="1" s="1"/>
+    <row r="76" ht="12" customHeight="1" s="1"/>
+    <row r="77" ht="12" customHeight="1" s="1"/>
+    <row r="78" ht="12" customHeight="1" s="1"/>
+    <row r="79" ht="12" customHeight="1" s="1"/>
+    <row r="80" ht="12" customHeight="1" s="1"/>
+    <row r="81" ht="12" customHeight="1" s="1"/>
+    <row r="82" ht="12" customHeight="1" s="1"/>
+    <row r="83" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
